--- a/docs/Logic Requirements/Ageipelago Civ Restrictions.xlsx
+++ b/docs/Logic Requirements/Ageipelago Civ Restrictions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{922C4411-90B7-4799-8758-5455A83749A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88B0FF2-0A50-42A4-974E-BFAEC56CC10F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28020" yWindow="1260" windowWidth="27750" windowHeight="13740" firstSheet="45" activeTab="55" xr2:uid="{02993E3C-F9A8-446E-907A-FAA48CE49BAD}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="41" activeTab="51" xr2:uid="{02993E3C-F9A8-446E-907A-FAA48CE49BAD}"/>
   </bookViews>
   <sheets>
     <sheet name="Armenians" sheetId="1" r:id="rId1"/>
@@ -255,11 +255,6 @@
 Two-Man Saw</t>
   </si>
   <si>
-    <t>Houfnice
-Hussite Wagon
-Elite Hussite Wagon</t>
-  </si>
-  <si>
     <t>Wagenburg Tactics
 Hussite Reforms</t>
   </si>
@@ -298,24 +293,6 @@
 Composite Bowman
 Elite Composite Bowman
 Warrior Monk</t>
-  </si>
-  <si>
-    <t>Hand Connoneer
-Hussar
-Paladins
-Siege Ram
-Siege Onagers
-Bombard Cannons
-Elite Cannon Galleon
-Carrack</t>
-  </si>
-  <si>
-    <t>Longbowman
-Elite Longbowman</t>
-  </si>
-  <si>
-    <t>Yeomen
-Warwolf</t>
   </si>
   <si>
     <t>Thumb Ring
@@ -380,14 +357,6 @@
     <t>Cavalier available in Castle Age</t>
   </si>
   <si>
-    <t>Arbalester
-Heavy Cavalry Archer
-Siege Ram
-Siege Onager
-Heavy Scorpion
-Heavy Demolition Ship</t>
-  </si>
-  <si>
     <t>Burgundian Vineyards
 Flemish Revolution</t>
   </si>
@@ -473,22 +442,6 @@
 Incendiaries
 Sappers
 Herbal Medicine</t>
-  </si>
-  <si>
-    <t>Coustillier
-Elite Coustillier
-Flemish Militia</t>
-  </si>
-  <si>
-    <t>Arbalester
-Hand Cannoneer
-Bombard Cannon
-Elite Cannon Galleon
-Fast Fire Ship</t>
-  </si>
-  <si>
-    <t>Woad Raider
-Elite Woad Raider</t>
   </si>
   <si>
     <t>Strongholds
@@ -719,47 +672,9 @@
 Heavy Demolition Ship</t>
   </si>
   <si>
-    <t>Fortified Wall
-Keep
-Bombard Tower</t>
-  </si>
-  <si>
     <t>Cranequins
 Hamask
 Northmen's Fury</t>
-  </si>
-  <si>
-    <t>Parthian Tactics
-Architecture
-Fortified Wall
-Bombard Tower
-Keep
-Siphons
-Invendiaries
-Treadmill Crane
-Sappers
-Faith
-Atonement
-Herbal Medicine
-Heresy
-Two-Man Saw
-Guilds
-Crop Rotation</t>
-  </si>
-  <si>
-    <t>Arbalester
-Hussar
-Siege Ram
-Siege Onager
-Elite Cannon Galleon</t>
-  </si>
-  <si>
-    <t>Throwing Axeman
-Elite Throwing Axeman</t>
-  </si>
-  <si>
-    <t>Bearded Axe
-Chivalry</t>
   </si>
   <si>
     <t>Thumb Ring
@@ -1085,32 +1000,6 @@
   </si>
   <si>
     <t>Condottiero available to all Allies</t>
-  </si>
-  <si>
-    <t>Heavy Cavalry Archer
-Halberdier
-Paladin
-Siege Ram
-Siege Onager
-Heavy Scorpion
-Heavy Demolition Ship</t>
-  </si>
-  <si>
-    <t>Condottiero
-Genoese Crossbowman
-Elite Genoese Crossbowman</t>
-  </si>
-  <si>
-    <t>Parthian Tactics
-Gambersons
-Siege Engineers
-Sappers</t>
-  </si>
-  <si>
-    <t>Silk Road
-Pitotechnia
-Heresy
-Gold Shaft Mining</t>
   </si>
   <si>
     <t>Hussar
@@ -1827,21 +1716,6 @@
     <t>Folwark</t>
   </si>
   <si>
-    <t>Hand Cannoneer
-Halberdier
-Hussar
-Paladin
-Siege Onager
-Heavy Scorpion
-Elite Cannon Galleon
-Heavy Demolition Ship</t>
-  </si>
-  <si>
-    <t>Winged Hussar
-Obuch
-Elite Obuch</t>
-  </si>
-  <si>
     <t>Szlachta Privilges
 Lechitic Legacy</t>
   </si>
@@ -1873,26 +1747,8 @@
     <t>Feitoria</t>
   </si>
   <si>
-    <t>Organ Gun
-Elite Organ Gun
-Caravel
-Elite Caravel</t>
-  </si>
-  <si>
     <t>Circumnavigation
 Arquebus</t>
-  </si>
-  <si>
-    <t>Heavy Cavalry Archer
-Hussar
-Paladin
-Siege Ram
-Siege Onager
-Heavy Scorpion
-Fast Fire Ship
-Demolition Raft
-Demolition Ship
-Heavy Demolition Ship</t>
   </si>
   <si>
     <t>Parthian Tactics
@@ -2046,28 +1902,12 @@
 Shield Wall</t>
   </si>
   <si>
-    <t>Hand Cannoneer
-Heavy Cavalry Archer
-Hussar
-Paladin
-Bombard Cannon
-Elite Cannon Galleon</t>
-  </si>
-  <si>
     <t>Watch Tower
 Guard Tower
 Keep
 Bombard Tower
 Fortified Wall
 Fortified Gate</t>
-  </si>
-  <si>
-    <t>Serjeant
-Elite Serjeant</t>
-  </si>
-  <si>
-    <t>First Crusade
-Hauberk</t>
   </si>
   <si>
     <t>Donjon</t>
@@ -2131,19 +1971,8 @@
 Guilds</t>
   </si>
   <si>
-    <t>Crossbowman
-Arbalester
-Siege Onager
-Heavy Scorpion</t>
-  </si>
-  <si>
     <t>Inquisition
 Supremacy</t>
-  </si>
-  <si>
-    <t>Conquistador
-Elite Conquistador
-Missionary</t>
   </si>
   <si>
     <t>Parthian Tactics
@@ -2205,20 +2034,8 @@
     <t>Murder Holes and Herbal Medicine are researched automatically</t>
   </si>
   <si>
-    <t>Teutonic Knight
-Elite Teutonic Knight</t>
-  </si>
-  <si>
     <t>Ironclad
 Crenellations</t>
-  </si>
-  <si>
-    <t>Arbalester
-Heavy Cavalry Archer
-Light Cavalry
-Hussar
-Siege Ram
-Elite Cannon Galleon</t>
   </si>
   <si>
     <t>Thumb Ring
@@ -2391,31 +2208,9 @@
 Heavy Demolition Ship</t>
   </si>
   <si>
-    <t>Blast Furnace
-Plate Barding Armor
-Bombard Tower
-Clinker Construction
-Carvel Hull
-Incendiaries
-Fervor
-Stone Shaft Mining</t>
-  </si>
-  <si>
     <t>Cranequins
 Vendel Legacy
 Gothikon</t>
-  </si>
-  <si>
-    <t>Blast Furnace
-Plate Barding Armor
-Bombard Tower
-Keep
-Arrowslits
-Redemption
-Block Printing
-Heresy
-Sanctity
-Gold Shaft Mining</t>
   </si>
   <si>
     <t>Imperial Skirmisher available for all Allies</t>
@@ -2455,45 +2250,8 @@
 Gold Shaft Mining</t>
   </si>
   <si>
-    <t>Hand Cannoneer
-Heavy Cavalry Archer
-Halberdier
-Hussar
-Paladin
-Siege Onager
-Bombard Cannon
-Fast Fire Ship
-Demolition Raft
-Demolition Ship
-Heavy Demolition Ship</t>
-  </si>
-  <si>
-    <t>Longboat
-Elite Longboat
-Berserk
-Elite Berserk</t>
-  </si>
-  <si>
     <t>Chieftains
 Bogsveigar</t>
-  </si>
-  <si>
-    <t>Thumb Ring
-Parthian Tactics
-Bloodlines
-Husbandry
-Plate Barding Armor
-Bombard Tower
-Keep
-Shipwright
-Incendiaries
-Illumination
-Redemption
-Theocracy
-Herbal Medicine
-Sanctity
-Stone Shaft Mining
-Guilds</t>
   </si>
   <si>
     <t>Tiger Cavalry
@@ -2588,6 +2346,294 @@
 Block Printing
 Heresy
 Crop Rotation</t>
+  </si>
+  <si>
+    <t>Houfnice
+Hussite Wagon
+Elite Hussite Wagon
+Mounted Crossbowman</t>
+  </si>
+  <si>
+    <t>Longbowman
+Elite Longbowman
+Mounted Crossbowman
+Heavy Mounted Crossbowman</t>
+  </si>
+  <si>
+    <t>Yeomen
+Warwolf
+Cranequins</t>
+  </si>
+  <si>
+    <t>Hand Connoneer
+Cavalry Archer
+Heavy Cavalry Archer
+Hussar
+Paladins
+Siege Ram
+Siege Onagers
+Bombard Cannons
+Elite Cannon Galleon
+Carrack</t>
+  </si>
+  <si>
+    <t>Arbalester
+Cavalry Archer
+Heavy Cavalry Archer
+Siege Ram
+Siege Onager
+Heavy Scorpion
+Heavy Demolition Ship</t>
+  </si>
+  <si>
+    <t>Coustillier
+Elite Coustillier
+Flemish Militia
+Mounted Crossbowman</t>
+  </si>
+  <si>
+    <t>Woad Raider
+Elite Woad Raider
+Mounted Crossbowman
+Heavy Mounted Crossbowman</t>
+  </si>
+  <si>
+    <t>Arbalester
+Cavalry Archer
+Heavy Cavalry Archer
+Hand Cannoneer
+Bombard Cannon
+Elite Cannon Galleon
+Fast Fire Ship</t>
+  </si>
+  <si>
+    <t>Parthian Tactics
+Architecture
+Fortified Wall
+Bombard Tower
+Siphons
+Invendiaries
+Treadmill Crane
+Sappers
+Faith
+Atonement
+Herbal Medicine
+Heresy
+Two-Man Saw
+Guilds
+Crop Rotation</t>
+  </si>
+  <si>
+    <t>Fortified Wall
+Bombard Tower</t>
+  </si>
+  <si>
+    <t>Throwing Axeman
+Elite Throwing Axeman
+Mounted Crossbowman
+Heavy Mounted Crossbowman</t>
+  </si>
+  <si>
+    <t>Arbalester
+Cavalry Archer
+Heavy Cavalry Archer
+Hussar
+Siege Ram
+Siege Onager
+Elite Cannon Galleon</t>
+  </si>
+  <si>
+    <t>Cranequins
+Ordonnance Companies
+Chivalry</t>
+  </si>
+  <si>
+    <t>Cavalry Archer
+Heavy Cavalry Archer
+Halberdier
+Paladin
+Siege Ram
+Siege Onager
+Heavy Scorpion
+Heavy Demolition Ship</t>
+  </si>
+  <si>
+    <t>Condottiero
+Genoese Crossbowman
+Elite Genoese Crossbowman
+Mounted Crossbowman</t>
+  </si>
+  <si>
+    <t>Silk Road
+Pitotechnia
+Heresy</t>
+  </si>
+  <si>
+    <t>Parthian Tactics
+Gambersons
+Siege Engineers
+Sappers
+Gold Shaft Mining</t>
+  </si>
+  <si>
+    <t>Hand Cannoneer
+Cavalry Archer
+Heavy Cavalry Archer
+Halberdier
+Hussar
+Paladin
+Siege Onager
+Heavy Scorpion
+Elite Cannon Galleon
+Heavy Demolition Ship</t>
+  </si>
+  <si>
+    <t>Winged Hussar
+Obuch
+Elite Obuch
+Mounted Crossbowman
+Heavy Mounted Crossbowman</t>
+  </si>
+  <si>
+    <t>Cavalry Archer
+Heavy Cavalry Archer
+Hussar
+Paladin
+Siege Ram
+Siege Onager
+Heavy Scorpion
+Fast Fire Ship
+Demolition Raft
+Demolition Ship
+Heavy Demolition Ship</t>
+  </si>
+  <si>
+    <t>Organ Gun
+Elite Organ Gun
+Caravel
+Elite Caravel
+Mounted Crossbowman</t>
+  </si>
+  <si>
+    <t>Parthian Tactics
+Blast Furnace
+Plate Barding Armor
+Bombard Tower
+Clinker Construction
+Carvel Hull
+Incendiaries
+Fervor
+Stone Shaft Mining</t>
+  </si>
+  <si>
+    <t>Hand Cannoneer
+Cavalry Archer
+Heavy Cavalry Archer
+Hussar
+Paladin
+Bombard Cannon
+Elite Cannon Galleon</t>
+  </si>
+  <si>
+    <t>Cranequins
+First Crusade
+Hauberk</t>
+  </si>
+  <si>
+    <t>Serjeant
+Elite Serjeant
+Mounted Crossbowman
+Heavy Mounted Crossbowman</t>
+  </si>
+  <si>
+    <t>Crossbowman
+Cavalry Archer
+Heavy Cavalry Archer
+Arbalester
+Siege Onager
+Heavy Scorpion</t>
+  </si>
+  <si>
+    <t>Conquistador
+Elite Conquistador
+Missionary
+Mounted Crossbowman
+Heavy Mounted Crossbowman</t>
+  </si>
+  <si>
+    <t>Teutonic Knight
+Elite Teutonic Knight
+Mounted Crossbowman
+Heavy Mounted Crossbowman</t>
+  </si>
+  <si>
+    <t>Arbalester
+Cavalry Archer
+Heavy Cavalry Archer
+Light Cavalry
+Hussar
+Siege Ram
+Elite Cannon Galleon</t>
+  </si>
+  <si>
+    <t>Thumb Ring
+Parthian Tactics
+Gambersons
+Bloodlines
+Husbandry
+Plate Barding Armor
+Bombard Tower
+Keep
+Shipwright
+Incendiaries
+Illumination
+Redemption
+Theocracy
+Herbal Medicine
+Sanctity
+Stone Shaft Mining
+Guilds</t>
+  </si>
+  <si>
+    <t>Longboat
+Elite Longboat
+Berserk
+Elite Berserk
+Mounted Crossbowman
+Heavy Mounted Crossbowman
+Varangian Guard
+Elite Varangian Guard
+Catapult Galleon</t>
+  </si>
+  <si>
+    <t>Hand Cannoneer
+Cavalry Archer
+Heavy Cavalry Archer
+Halberdier
+Hussar
+Paladin
+Siege Onager
+Bombard Cannon
+Fast Fire Ship
+Demolition Raft
+Demolition Ship
+Heavy Demolition Ship
+Cannon Galleon
+Elite Cannon Galleon</t>
+  </si>
+  <si>
+    <t>Thumb Ring
+Parthian Tactics
+Bombard Tower
+Keep
+Arrowslits
+Hoardings
+Sappers
+Redemption
+Block Printing
+Heresy
+Sanctity
+Gold Shaft Mining</t>
   </si>
 </sst>
 </file>
@@ -2720,6 +2766,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2728,9 +2777,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3062,21 +3108,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -3109,7 +3155,7 @@
     </row>
     <row r="5" spans="2:12" ht="243.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>7</v>
@@ -3118,10 +3164,10 @@
         <v>9</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>8</v>
@@ -3131,7 +3177,7 @@
         <v>6</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -3162,21 +3208,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -3210,17 +3256,17 @@
     <row r="5" spans="2:12" ht="187.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -3254,21 +3300,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -3304,17 +3350,17 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>57</v>
+        <v>274</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>58</v>
+        <v>273</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -3348,21 +3394,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -3396,17 +3442,17 @@
     <row r="5" spans="2:12" ht="206.25" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -3440,21 +3486,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -3487,26 +3533,26 @@
     </row>
     <row r="5" spans="2:12" ht="393.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="L5" s="2"/>
     </row>
@@ -3539,21 +3585,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -3586,20 +3632,20 @@
     </row>
     <row r="5" spans="2:12" ht="318.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>84</v>
+        <v>275</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -3633,21 +3679,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -3681,17 +3727,17 @@
     <row r="5" spans="2:12" ht="281.25" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -3725,21 +3771,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -3775,21 +3821,21 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="L5" s="2"/>
     </row>
@@ -3821,21 +3867,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -3871,22 +3917,22 @@
         <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>85</v>
+        <v>278</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>86</v>
+        <v>277</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>87</v>
+        <v>279</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -3917,21 +3963,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -3964,27 +4010,27 @@
     </row>
     <row r="5" spans="2:12" ht="243.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -4015,21 +4061,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -4062,27 +4108,27 @@
     </row>
     <row r="5" spans="2:12" ht="393.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -4113,21 +4159,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -4166,11 +4212,11 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>11</v>
@@ -4207,21 +4253,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -4257,17 +4303,17 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -4301,21 +4347,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -4351,19 +4397,19 @@
         <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -4397,21 +4443,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -4444,24 +4490,24 @@
     </row>
     <row r="5" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="L5" s="2"/>
     </row>
@@ -4493,21 +4539,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -4540,29 +4586,29 @@
     </row>
     <row r="5" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>264</v>
+        <v>236</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -4593,21 +4639,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -4638,24 +4684,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="168.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="187.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>126</v>
+        <v>280</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>128</v>
+        <v>283</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>127</v>
+        <v>281</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>129</v>
+        <v>282</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="L5" s="2"/>
     </row>
@@ -4687,21 +4733,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -4737,19 +4783,19 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="I5" s="6"/>
+        <v>115</v>
+      </c>
+      <c r="I5" s="3"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -4782,21 +4828,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -4832,22 +4878,22 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
@@ -4878,21 +4924,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -4925,26 +4971,26 @@
     </row>
     <row r="5" spans="2:12" ht="318.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>141</v>
+        <v>124</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>143</v>
+        <v>126</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>139</v>
+        <v>122</v>
       </c>
       <c r="L5" s="2"/>
     </row>
@@ -4976,21 +5022,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -5026,24 +5072,24 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>151</v>
+        <v>134</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -5074,21 +5120,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -5122,22 +5168,22 @@
     <row r="5" spans="2:12" ht="206.25" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>154</v>
+        <v>137</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -5168,21 +5214,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -5262,21 +5308,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -5310,17 +5356,17 @@
     <row r="5" spans="2:12" ht="206.25" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -5354,21 +5400,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -5401,25 +5447,25 @@
     </row>
     <row r="5" spans="2:12" ht="300" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -5450,21 +5496,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -5497,29 +5543,29 @@
     </row>
     <row r="5" spans="2:12" ht="300" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>167</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -5550,21 +5596,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -5600,17 +5646,17 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -5644,21 +5690,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -5691,29 +5737,29 @@
     </row>
     <row r="5" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -5744,21 +5790,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -5791,20 +5837,20 @@
     </row>
     <row r="5" spans="2:12" ht="375" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -5838,21 +5884,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -5885,20 +5931,20 @@
     </row>
     <row r="5" spans="2:12" ht="375" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -5932,21 +5978,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -5979,27 +6025,27 @@
     </row>
     <row r="5" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>266</v>
+        <v>238</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -6030,21 +6076,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -6077,27 +6123,27 @@
     </row>
     <row r="5" spans="2:12" ht="243.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -6128,21 +6174,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -6175,29 +6221,29 @@
     </row>
     <row r="5" spans="2:12" ht="300" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>212</v>
+        <v>284</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>215</v>
+        <v>196</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>213</v>
+        <v>285</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -6228,21 +6274,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -6324,21 +6370,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -6369,22 +6415,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="225" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="243.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>221</v>
+        <v>286</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>219</v>
+        <v>287</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -6418,21 +6464,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -6468,17 +6514,17 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -6512,21 +6558,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -6562,17 +6608,17 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -6606,21 +6652,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -6656,17 +6702,17 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -6700,21 +6746,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -6747,17 +6793,17 @@
     </row>
     <row r="5" spans="2:12" ht="262.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
       <c r="H5" s="2"/>
       <c r="J5" s="2"/>
@@ -6792,21 +6838,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -6839,26 +6885,26 @@
     </row>
     <row r="5" spans="2:12" ht="300" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>237</v>
+        <v>289</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>241</v>
+        <v>217</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>239</v>
+        <v>291</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="L5" s="2"/>
     </row>
@@ -6890,21 +6936,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -6937,25 +6983,25 @@
     </row>
     <row r="5" spans="2:12" ht="300" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>245</v>
+        <v>221</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>248</v>
+        <v>224</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>247</v>
+        <v>223</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>244</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -6986,21 +7032,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -7034,17 +7080,17 @@
     <row r="5" spans="2:12" ht="131.25" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>249</v>
+        <v>292</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>251</v>
+        <v>293</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -7078,21 +7124,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -7125,25 +7171,25 @@
     </row>
     <row r="5" spans="2:12" ht="318.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>257</v>
+        <v>231</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>254</v>
+        <v>228</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>253</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -7174,21 +7220,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -7222,22 +7268,22 @@
     <row r="5" spans="2:12" ht="187.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>262</v>
+        <v>295</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>263</v>
+        <v>235</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>260</v>
+        <v>294</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>261</v>
+        <v>234</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>259</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -7268,21 +7314,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -7316,24 +7362,24 @@
     <row r="5" spans="2:12" ht="225" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -7364,21 +7410,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -7411,27 +7457,27 @@
     </row>
     <row r="5" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>268</v>
+        <v>240</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>267</v>
+        <v>239</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>269</v>
+        <v>241</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>270</v>
+        <v>242</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>272</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -7462,21 +7508,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -7510,22 +7556,22 @@
     <row r="5" spans="2:12" ht="150" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>276</v>
+        <v>248</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>275</v>
+        <v>247</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>274</v>
+        <v>246</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>273</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -7556,21 +7602,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -7603,20 +7649,20 @@
     </row>
     <row r="5" spans="2:12" ht="300" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>281</v>
+        <v>252</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -7650,21 +7696,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -7698,21 +7744,21 @@
     <row r="5" spans="2:12" ht="225" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>286</v>
+        <v>256</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>287</v>
+        <v>257</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>285</v>
+        <v>255</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>284</v>
+        <v>254</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="L5" s="2"/>
     </row>
@@ -7744,21 +7790,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -7789,22 +7835,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="318.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="337.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>290</v>
+        <v>258</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -7838,21 +7884,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -7888,17 +7934,17 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>295</v>
+        <v>262</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>294</v>
+        <v>261</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>292</v>
+        <v>259</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>293</v>
+        <v>260</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -7932,21 +7978,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -7979,20 +8025,20 @@
     </row>
     <row r="5" spans="2:12" ht="281.25" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>296</v>
+        <v>263</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>299</v>
+        <v>266</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>297</v>
+        <v>264</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>298</v>
+        <v>265</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -8026,21 +8072,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -8071,22 +8117,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="168.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="225" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>270</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>32</v>
+        <v>268</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>33</v>
+        <v>269</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -8120,21 +8166,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -8167,27 +8213,27 @@
     </row>
     <row r="5" spans="2:12" ht="300" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -8218,21 +8264,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -8266,24 +8312,24 @@
     <row r="5" spans="2:12" ht="337.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>43</v>
+        <v>271</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>56</v>
+        <v>272</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -8314,21 +8360,21 @@
   <sheetData>
     <row r="2" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="2:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5"/>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="5"/>
+      <c r="D3" s="6"/>
+      <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="5"/>
-      <c r="J3" s="3" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="6"/>
+      <c r="J3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -8364,22 +8410,22 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Logic Requirements/Ageipelago Civ Restrictions.xlsx
+++ b/docs/Logic Requirements/Ageipelago Civ Restrictions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88B0FF2-0A50-42A4-974E-BFAEC56CC10F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D1BC11-C5D1-44CE-94C2-43EDE9D4B03C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="41" activeTab="51" xr2:uid="{02993E3C-F9A8-446E-907A-FAA48CE49BAD}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="9" xr2:uid="{02993E3C-F9A8-446E-907A-FAA48CE49BAD}"/>
   </bookViews>
   <sheets>
     <sheet name="Armenians" sheetId="1" r:id="rId1"/>
@@ -421,13 +421,6 @@
 Elite Cannon Galleons</t>
   </si>
   <si>
-    <t>Camel Rider
-Heavy Camel Rider
-Dromon
-Cataphract
-Elite Cataphract</t>
-  </si>
-  <si>
     <t>Greek Fire
 Logistica</t>
   </si>
@@ -2634,6 +2627,15 @@
 Heresy
 Sanctity
 Gold Shaft Mining</t>
+  </si>
+  <si>
+    <t>Camel Rider
+Heavy Camel Rider
+Dromon
+Cataphract
+Elite Cataphract
+Varangian Guard
+Elite Varangian Guard</t>
   </si>
 </sst>
 </file>
@@ -3155,7 +3157,7 @@
     </row>
     <row r="5" spans="2:12" ht="243.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>7</v>
@@ -3164,7 +3166,7 @@
         <v>9</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>29</v>
@@ -3177,7 +3179,7 @@
         <v>6</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -3259,14 +3261,14 @@
         <v>47</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -3350,17 +3352,17 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -3442,17 +3444,17 @@
     <row r="5" spans="2:12" ht="206.25" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -3533,26 +3535,26 @@
     </row>
     <row r="5" spans="2:12" ht="393.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="J5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="L5" s="2"/>
     </row>
@@ -3632,20 +3634,20 @@
     </row>
     <row r="5" spans="2:12" ht="318.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -3727,17 +3729,17 @@
     <row r="5" spans="2:12" ht="281.25" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -3821,21 +3823,21 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L5" s="2"/>
     </row>
@@ -3917,22 +3919,22 @@
         <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -4010,27 +4012,27 @@
     </row>
     <row r="5" spans="2:12" ht="243.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -4108,27 +4110,27 @@
     </row>
     <row r="5" spans="2:12" ht="393.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -4212,11 +4214,11 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>11</v>
@@ -4303,17 +4305,17 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -4397,19 +4399,19 @@
         <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -4490,24 +4492,24 @@
     </row>
     <row r="5" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L5" s="2"/>
     </row>
@@ -4586,29 +4588,29 @@
     </row>
     <row r="5" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="J5" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -4687,21 +4689,21 @@
     <row r="5" spans="2:12" ht="187.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L5" s="2"/>
     </row>
@@ -4783,17 +4785,17 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="2"/>
@@ -4878,22 +4880,22 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -4971,26 +4973,26 @@
     </row>
     <row r="5" spans="2:12" ht="318.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="G5" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L5" s="2"/>
     </row>
@@ -5072,24 +5074,24 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="J5" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -5168,22 +5170,22 @@
     <row r="5" spans="2:12" ht="206.25" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -5356,17 +5358,17 @@
     <row r="5" spans="2:12" ht="206.25" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -5447,25 +5449,25 @@
     </row>
     <row r="5" spans="2:12" ht="300" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -5543,29 +5545,29 @@
     </row>
     <row r="5" spans="2:12" ht="300" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -5646,17 +5648,17 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -5737,29 +5739,29 @@
     </row>
     <row r="5" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="J5" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="L5" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -5837,20 +5839,20 @@
     </row>
     <row r="5" spans="2:12" ht="375" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -5931,20 +5933,20 @@
     </row>
     <row r="5" spans="2:12" ht="375" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -6025,27 +6027,27 @@
     </row>
     <row r="5" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>184</v>
-      </c>
       <c r="J5" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -6123,27 +6125,27 @@
     </row>
     <row r="5" spans="2:12" ht="243.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -6221,29 +6223,29 @@
     </row>
     <row r="5" spans="2:12" ht="300" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>195</v>
-      </c>
       <c r="J5" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -6418,19 +6420,19 @@
     <row r="5" spans="2:12" ht="243.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -6514,17 +6516,17 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -6608,17 +6610,17 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>209</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -6702,17 +6704,17 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>215</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -6793,17 +6795,17 @@
     </row>
     <row r="5" spans="2:12" ht="262.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H5" s="2"/>
       <c r="J5" s="2"/>
@@ -6885,26 +6887,26 @@
     </row>
     <row r="5" spans="2:12" ht="300" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="G5" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>290</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L5" s="2"/>
     </row>
@@ -6983,25 +6985,25 @@
     </row>
     <row r="5" spans="2:12" ht="300" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>223</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -7080,17 +7082,17 @@
     <row r="5" spans="2:12" ht="131.25" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -7171,25 +7173,25 @@
     </row>
     <row r="5" spans="2:12" ht="318.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>232</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -7268,22 +7270,22 @@
     <row r="5" spans="2:12" ht="187.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -7369,7 +7371,7 @@
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>24</v>
@@ -7457,27 +7459,27 @@
     </row>
     <row r="5" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>242</v>
-      </c>
       <c r="J5" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -7556,22 +7558,22 @@
     <row r="5" spans="2:12" ht="150" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>249</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -7649,20 +7651,20 @@
     </row>
     <row r="5" spans="2:12" ht="300" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -7744,21 +7746,21 @@
     <row r="5" spans="2:12" ht="225" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="L5" s="2"/>
     </row>
@@ -7837,20 +7839,20 @@
     </row>
     <row r="5" spans="2:12" ht="337.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -7934,17 +7936,17 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>259</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>260</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -8028,17 +8030,17 @@
         <v>33</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>265</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -8122,17 +8124,17 @@
         <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>268</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>269</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -8312,14 +8314,14 @@
     <row r="5" spans="2:12" ht="337.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>40</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>39</v>

--- a/docs/Logic Requirements/Ageipelago Civ Restrictions.xlsx
+++ b/docs/Logic Requirements/Ageipelago Civ Restrictions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D1BC11-C5D1-44CE-94C2-43EDE9D4B03C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{775B909A-19CE-49D1-B7D8-74ACCC4FDFAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="9" xr2:uid="{02993E3C-F9A8-446E-907A-FAA48CE49BAD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="42" activeTab="53" xr2:uid="{02993E3C-F9A8-446E-907A-FAA48CE49BAD}"/>
   </bookViews>
   <sheets>
     <sheet name="Armenians" sheetId="1" r:id="rId1"/>
@@ -133,20 +133,6 @@
 Fereters</t>
   </si>
   <si>
-    <t>Thumb Ring
-Parthian Tactics
-Architecture
-Siege Engineers
-Keep
-Arrowslits
-Shipwright
-Dry Dock
-Treadmill Crane
-Stone Shaft Mining
-Two-Man Saw
-Crop Rotation</t>
-  </si>
-  <si>
     <t>Stable
 Keep
 Bombard Tower</t>
@@ -206,17 +192,6 @@
 Mahayana</t>
   </si>
   <si>
-    <t>Thumb Ring
-Parthian Tactics
-Plate Mail Armor
-Bombard Tower
-Incendiaries
-Hoardings
-Sappers
-Heresy
-Stone Shaft Mining</t>
-  </si>
-  <si>
     <t>Genitour and Elite Genitour available for all Allies</t>
   </si>
   <si>
@@ -267,19 +242,6 @@
 Siege Onager
 Fast Fire Ship
 Heavy Demolition Ship</t>
-  </si>
-  <si>
-    <t>Thumb Ring
-Parthian Tactics
-Gambersons
-Bloodlines
-Plate Barding Armor
-Heated Shot
-Shipwright
-Dry Dock
-Carvel Hull
-Hoardings
-Crop Rotation</t>
   </si>
   <si>
     <t>Hand Cannoneer available in Castle Age</t>
@@ -439,37 +401,6 @@
   <si>
     <t>Strongholds
 Furor Celtica</t>
-  </si>
-  <si>
-    <t>Thumb Ring
-Parthian Tactics
-Squires
-Bloodlines
-Bracer
-Plate Barding Armor
-Architecture
-Bombard Tower
-Siphons
-Incendiaries
-Redemption
-Atonement
-Illumination
-Block Printing
-Theocracy
-Two-Man Saw
-Crop Rotation</t>
-  </si>
-  <si>
-    <t>Hand Cannoneer
-Hussar
-Paladin
-Mangonel
-Onager
-Siege Onager
-Bombard Cannon
-Cannon Galleon
-Elite Cannon Galleon
-Fast Fire Ship</t>
   </si>
   <si>
     <t>Fire Lancer
@@ -670,24 +601,6 @@
 Northmen's Fury</t>
   </si>
   <si>
-    <t>Thumb Ring
-Parthian Tactics
-Bloodlines
-Ring Archer Armor
-Bracer
-Bombard Tower
-Keep
-Heated Shot
-Shipwright
-Incendiaries
-Treadmill Crane
-Redemption
-Atonement
-Stone Shaft Mining
-Two-Man Saw
-Guilds</t>
-  </si>
-  <si>
     <t>Keep
 Lumber Camp
 Mining Camp
@@ -774,28 +687,6 @@
   <si>
     <t>Anarchy
 Perfusion</t>
-  </si>
-  <si>
-    <t>Thumb Ring
-Parthian Tactics
-Arson
-Gambersons
-Plate Barding Armor
-Plate Mail Armor
-Fortified Wall
-Bombard Tower
-Siege Engineers
-Guard Tower
-Keep
-Arrowslits
-Dry Dock
-Treadmill Crane
-Hoardings
-Redemption
-Block Printing
-Atonement
-Heresy
-Gold Shaft Mining</t>
   </si>
   <si>
     <t>Arbalester
@@ -1200,19 +1091,6 @@
   <si>
     <t>Padded Archer Armor, Leather Archer Armor and Ring Archer Armor are researched automatically
 Bombard Tower is researched with Chemistry</t>
-  </si>
-  <si>
-    <t>Parthian Tactics
-Bloodlines
-Blast Furnace
-Plate Mail Armor
-Hoardings
-Sappers
-Illumination
-Redemption
-Atonement
-Heresy
-Crop Rotation</t>
   </si>
   <si>
     <t>Arbalester
@@ -1744,16 +1622,6 @@
 Arquebus</t>
   </si>
   <si>
-    <t>Parthian Tactics
-Squires
-Arrowslits
-Shipwright
-Incendiaries
-Hoardings
-Illumination
-Gold Shaft Mining</t>
-  </si>
-  <si>
     <t>Arbalester
 Hand Cannoneer
 Two-Handed Swordsman
@@ -1816,15 +1684,6 @@
 Fast Fire Ship</t>
   </si>
   <si>
-    <t>Architecture
-Bombard Tower
-Heated Shot
-Shipwright
-Stone Shaft Mining
-Guilds
-Crop Rotation</t>
-  </si>
-  <si>
     <t>Hand Cannoneer
 Hussar
 Knight
@@ -1847,22 +1706,6 @@
 White Feather Guard
 Elite White Feather Guard
 Liu Bei</t>
-  </si>
-  <si>
-    <t>Bloodlines
-Iron Casting
-Blast Furnace
-Bombard Tower
-Keep
-Siphon
-Incendiaries
-Treadmill Crane
-Redemption
-Block Printing
-Herbal Medicine
-Sanctity
-Stone Shaft Mining
-Crop Rotation</t>
   </si>
   <si>
     <t>Hand Cannoneer
@@ -2230,19 +2073,6 @@
 Fast Fire Ship</t>
   </si>
   <si>
-    <t>Parthian Tactics
-GambersonsBlast Furnace
-Masonry
-Architecture
-Shipwright
-Siphons
-Incendiaries
-Redemption
-Heresy
-Fervor
-Gold Shaft Mining</t>
-  </si>
-  <si>
     <t>Chieftains
 Bogsveigar</t>
   </si>
@@ -2636,6 +2466,178 @@
 Elite Cataphract
 Varangian Guard
 Elite Varangian Guard</t>
+  </si>
+  <si>
+    <t>Thumb Ring
+Parthian Tactics
+Architecture
+Siege Engineers
+Keep
+Arrowslits
+Shipwright
+Dry Dock
+Stone Shaft Mining
+Two-Man Saw
+Crop Rotation</t>
+  </si>
+  <si>
+    <t>Thumb Ring
+Parthian Tactics
+Plate Mail Armor
+Bombard Tower
+Incendiaries
+Treadmill Crane
+Hoardings
+Sappers
+Heresy
+Stone Shaft Mining</t>
+  </si>
+  <si>
+    <t>Thumb Ring
+Parthian Tactics
+Gambersons
+Bloodlines
+Plate Barding Armor
+Heated Shot
+Shipwright
+Dry Dock
+Carvel Hull
+Hoardings
+Treadmill Crane
+Crop Rotation</t>
+  </si>
+  <si>
+    <t>Thumb Ring
+Parthian Tactics
+Squires
+Bloodlines
+Bracer
+Plate Barding Armor
+Architecture
+Bombard Tower
+Siphons
+Incendiaries
+Treadmill Crane
+Redemption
+Atonement
+Illumination
+Block Printing
+Theocracy
+Two-Man Saw
+Crop Rotation</t>
+  </si>
+  <si>
+    <t>Hand Cannoneer
+Heavy Cavalry Archer
+Hussar
+Paladin
+Mangonel
+Onager
+Siege Onager
+Bombard Cannon
+Cannon Galleon
+Elite Cannon Galleon
+Fast Fire Ship</t>
+  </si>
+  <si>
+    <t>Thumb Ring
+Parthian Tactics
+Bloodlines
+Ring Archer Armor
+Bracer
+Bombard Tower
+Keep
+Heated Shot
+Shipwright
+Incendiaries
+Redemption
+Atonement
+Stone Shaft Mining
+Two-Man Saw
+Guilds</t>
+  </si>
+  <si>
+    <t>Thumb Ring
+Parthian Tactics
+Arson
+Gambersons
+Plate Barding Armor
+Plate Mail Armor
+Fortified Wall
+Bombard Tower
+Siege Engineers
+Guard Tower
+Keep
+Arrowslits
+Dry Dock
+Hoardings
+Redemption
+Block Printing
+Atonement
+Heresy
+Gold Shaft Mining</t>
+  </si>
+  <si>
+    <t>Parthian Tactics
+Gambersons
+Bloodlines
+Blast Furnace
+Plate Mail Armor
+Hoardings
+Sappers
+Illumination
+Redemption
+Atonement
+Heresy
+Crop Rotation</t>
+  </si>
+  <si>
+    <t>Parthian Tactics
+Squires
+Arrowslits
+Shipwright
+Incendiaries
+Hoardings
+Redemption
+Illumination
+Gold Shaft Mining</t>
+  </si>
+  <si>
+    <t>Architecture
+Bombard Tower
+Heated Shot
+Shipwright
+Treadmill Crane
+Stone Shaft Mining
+Guilds
+Crop Rotation</t>
+  </si>
+  <si>
+    <t>Bloodlines
+Iron Casting
+Blast Furnace
+Bombard Tower
+Keep
+Siphon
+Incendiaries
+Redemption
+Block Printing
+Herbal Medicine
+Sanctity
+Stone Shaft Mining
+Crop Rotation</t>
+  </si>
+  <si>
+    <t>Parthian Tactics
+GambersonsBlast Furnace
+Architecture
+Shipwright
+Siphons
+Incendiaries
+Redemption
+Heresy
+Fervor
+Gold Shaft Mining</t>
   </si>
 </sst>
 </file>
@@ -3157,19 +3159,19 @@
     </row>
     <row r="5" spans="2:12" ht="243.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>288</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>8</v>
@@ -3179,7 +3181,7 @@
         <v>6</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -3258,17 +3260,17 @@
     <row r="5" spans="2:12" ht="187.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -3347,22 +3349,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="337.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="356.25" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>51</v>
+        <v>291</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -3441,20 +3443,20 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="206.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="243.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>52</v>
+        <v>292</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -3535,26 +3537,26 @@
     </row>
     <row r="5" spans="2:12" ht="393.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>62</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="L5" s="2"/>
     </row>
@@ -3634,20 +3636,20 @@
     </row>
     <row r="5" spans="2:12" ht="318.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -3729,17 +3731,17 @@
     <row r="5" spans="2:12" ht="281.25" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -3820,24 +3822,24 @@
     </row>
     <row r="5" spans="2:12" ht="281.25" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="L5" s="2"/>
     </row>
@@ -3914,27 +3916,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="300" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="281.25" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>74</v>
+        <v>293</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -4012,27 +4014,27 @@
     </row>
     <row r="5" spans="2:12" ht="243.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -4108,29 +4110,29 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="393.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="375" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>90</v>
+        <v>294</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -4208,20 +4210,20 @@
     </row>
     <row r="5" spans="2:12" ht="393.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -4302,20 +4304,20 @@
     </row>
     <row r="5" spans="2:12" ht="318.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -4396,22 +4398,22 @@
     </row>
     <row r="5" spans="2:12" ht="337.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -4492,24 +4494,24 @@
     </row>
     <row r="5" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="L5" s="2"/>
     </row>
@@ -4588,29 +4590,29 @@
     </row>
     <row r="5" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -4689,21 +4691,21 @@
     <row r="5" spans="2:12" ht="187.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L5" s="2"/>
     </row>
@@ -4782,20 +4784,20 @@
     </row>
     <row r="5" spans="2:12" ht="187.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="2"/>
@@ -4877,25 +4879,25 @@
     </row>
     <row r="5" spans="2:12" ht="300" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -4973,26 +4975,26 @@
     </row>
     <row r="5" spans="2:12" ht="318.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="L5" s="2"/>
     </row>
@@ -5071,27 +5073,27 @@
     </row>
     <row r="5" spans="2:12" ht="281.25" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -5167,25 +5169,25 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="206.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="225" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>138</v>
+        <v>295</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -5263,20 +5265,20 @@
     </row>
     <row r="5" spans="2:12" ht="281.25" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>289</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -5358,17 +5360,17 @@
     <row r="5" spans="2:12" ht="206.25" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -5449,25 +5451,25 @@
     </row>
     <row r="5" spans="2:12" ht="300" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -5545,29 +5547,29 @@
     </row>
     <row r="5" spans="2:12" ht="300" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -5645,20 +5647,20 @@
     </row>
     <row r="5" spans="2:12" ht="225" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -5739,29 +5741,29 @@
     </row>
     <row r="5" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -5839,20 +5841,20 @@
     </row>
     <row r="5" spans="2:12" ht="375" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -5933,20 +5935,20 @@
     </row>
     <row r="5" spans="2:12" ht="375" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -6027,27 +6029,27 @@
     </row>
     <row r="5" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -6125,27 +6127,27 @@
     </row>
     <row r="5" spans="2:12" ht="243.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -6223,29 +6225,29 @@
     </row>
     <row r="5" spans="2:12" ht="300" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -6323,24 +6325,24 @@
     </row>
     <row r="5" spans="2:12" ht="187.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L5" s="2"/>
     </row>
@@ -6420,19 +6422,19 @@
     <row r="5" spans="2:12" ht="243.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>200</v>
+        <v>296</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -6513,20 +6515,20 @@
     </row>
     <row r="5" spans="2:12" ht="356.25" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -6605,22 +6607,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="131.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="150" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>208</v>
+        <v>297</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -6701,20 +6703,20 @@
     </row>
     <row r="5" spans="2:12" ht="281.25" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -6793,19 +6795,19 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="262.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="243.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>211</v>
+        <v>298</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="H5" s="2"/>
       <c r="J5" s="2"/>
@@ -6887,26 +6889,26 @@
     </row>
     <row r="5" spans="2:12" ht="300" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="L5" s="2"/>
     </row>
@@ -6985,25 +6987,25 @@
     </row>
     <row r="5" spans="2:12" ht="300" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -7082,17 +7084,17 @@
     <row r="5" spans="2:12" ht="131.25" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -7173,25 +7175,25 @@
     </row>
     <row r="5" spans="2:12" ht="318.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -7270,22 +7272,22 @@
     <row r="5" spans="2:12" ht="187.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -7361,27 +7363,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="225" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="243.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>26</v>
+        <v>290</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -7459,27 +7461,27 @@
     </row>
     <row r="5" spans="2:12" ht="409.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -7558,22 +7560,22 @@
     <row r="5" spans="2:12" ht="150" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -7651,20 +7653,20 @@
     </row>
     <row r="5" spans="2:12" ht="300" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -7743,24 +7745,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:12" ht="225" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" ht="206.25" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>256</v>
+        <v>299</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="L5" s="2"/>
     </row>
@@ -7839,20 +7841,20 @@
     </row>
     <row r="5" spans="2:12" ht="337.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -7933,20 +7935,20 @@
     </row>
     <row r="5" spans="2:12" ht="337.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -8027,20 +8029,20 @@
     </row>
     <row r="5" spans="2:12" ht="281.25" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -8121,20 +8123,20 @@
     </row>
     <row r="5" spans="2:12" ht="225" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -8215,27 +8217,27 @@
     </row>
     <row r="5" spans="2:12" ht="300" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="G5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -8314,24 +8316,24 @@
     <row r="5" spans="2:12" ht="337.5" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -8409,25 +8411,25 @@
     </row>
     <row r="5" spans="2:12" ht="243.75" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
